--- a/operational_taxonomy.xlsx
+++ b/operational_taxonomy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicbrennan/Documents/America/IGCC Fellowship/Taxonomy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151CA9E6-0664-9B4F-8D41-4E13B2B8BA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9049DD-647E-5149-B80F-3FB087F78F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Legend" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Taxonomy!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Taxonomy!$A$1:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vocab Mapping'!$A$1:$E$44</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="295">
   <si>
     <t>Group ID</t>
   </si>
@@ -145,9 +145,6 @@
     <t>Desensitization from false positives in AI-driven surveillance/alarm systems degrades response readiness.</t>
   </si>
   <si>
-    <t>seed_taxonomy “video surveillance” entry; WINS AI-in-physical-security workshops (2024)</t>
-  </si>
-  <si>
     <t>OP.G02</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>Controlled-environment measurement not yet validated against field conditions.</t>
   </si>
   <si>
-    <t>IAEA NR-T-1.26 §3.3.5 (data “category: artificial, laboratory, field”)</t>
-  </si>
-  <si>
     <t>OP.C0201.05</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>Small-data / low base-rate problem</t>
   </si>
   <si>
-    <t>Nuclear's low-frequency event base structurally limits representativeness independent of provenance.</t>
-  </si>
-  <si>
     <t>IAEA NR-T-1.26 §2.2.2</t>
   </si>
   <si>
@@ -250,9 +241,6 @@
     <t>Data unavailable or corrupted for non-adversarial reasons, undermining model input continuity.</t>
   </si>
   <si>
-    <t>IAEA NR-T-1.26 §4 (data considerations)</t>
-  </si>
-  <si>
     <t>OP.G03</t>
   </si>
   <si>
@@ -322,9 +310,6 @@
     <t>Content fidelity failure</t>
   </si>
   <si>
-    <t>Umbrella for non-adversarial failures in the fidelity of AI-generated or AI-processed content -- distinct from OP.C0301 (training-objective misalignment) and OP.C0304 (out-of-distribution/generalization failure). Added Aug 2026 to close a gap left when AVID (this project's former third framework, which covered content-quality issues via E0402/P0204) was retired without replacement.</t>
-  </si>
-  <si>
     <t>Ji, Lee, Frieske, et al. (2023), "Survey of Hallucination in Natural Language Generation," ACM Computing Surveys 55(12) Art. 248</t>
   </si>
   <si>
@@ -334,9 +319,6 @@
     <t xml:space="preserve">    Hallucination or misattribution</t>
   </si>
   <si>
-    <t>AI-generated content that is factually wrong, fabricated, or attributed to the wrong source/component -- consolidates four near-duplicate seed-taxonomy phrasings (misaligned/hallucinatory documentation or information; misinterpretation, hallucination, and misalignment; model misalignment, hallucination, and misattribution) into one canonical category.</t>
-  </si>
-  <si>
     <t>Ji, Lee, Frieske, et al. (2023), ACM Computing Surveys 55(12) Art. 248</t>
   </si>
   <si>
@@ -535,9 +517,6 @@
     <t>A bias or fault in one component spreads to coupled components within a single system architecture.</t>
   </si>
   <si>
-    <t>seed_taxonomy “fault/bias propagation” entries</t>
-  </si>
-  <si>
     <t>OP.G07</t>
   </si>
   <si>
@@ -601,9 +580,6 @@
     <t xml:space="preserve">    Material substitution</t>
   </si>
   <si>
-    <t>Covertly diverting nuclear material by substituting or supplementing the material stock with a close copy that can subvert probabilistic detection measures. Kept in this taxonomy despite being a deliberate act because it is a physical-domain technique with no home in ATLAS (attacks on AI models) or AVID (AI system CIA) as currently scoped.</t>
-  </si>
-  <si>
     <t>IAEA NR-T-1.26</t>
   </si>
   <si>
@@ -874,9 +850,6 @@
     <t>Parasuraman, R. &amp; Manzey, D.H. (2010). “Complacency and Bias in Human Use of Automation.” Human Factors, 52(3) — peer-reviewed. Slattery, P. et al. (2024). “The AI Risk Repository.” Patterns, Cell Press — peer-reviewed. WINS AI-in-physical-security workshop series (2024).</t>
   </si>
   <si>
-    <t>The model is generalized across a range of operating scenarios for which the data quality and hence model efficiency or alignment is heterogeneous.</t>
-  </si>
-  <si>
     <t>IAEA NR-T-1.26 §2.1.3. AVID P0101</t>
   </si>
   <si>
@@ -890,6 +863,24 @@
   </si>
   <si>
     <t xml:space="preserve">    Data / Operational drift</t>
+  </si>
+  <si>
+    <t>OP.C0302.03</t>
+  </si>
+  <si>
+    <t>Input distribution shifts from the training distribution. This may be due to the operations of the system changing or expanding without model re-qualification. Examples include power uprates, load following, inter-reactor shuffling, new fuels, etc.</t>
+  </si>
+  <si>
+    <t>OP.C0703</t>
+  </si>
+  <si>
+    <t>WINS AI-in-physical-security workshops (2024)</t>
+  </si>
+  <si>
+    <t>Nuclear's low-frequency event base structurally limits representativeness independent of provenance. Data scarcity -- paralleled in OP.C0701 for nuclear safeguards-specific data.</t>
+  </si>
+  <si>
+    <t>IAEA NR-T-1.26 §4</t>
   </si>
   <si>
     <r>
@@ -912,17 +903,35 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> equipment ageing.</t>
+      <t>equipment ageing.</t>
     </r>
   </si>
   <si>
-    <t>OP.C0302.03</t>
-  </si>
-  <si>
-    <t>Input distribution shifts from the training distribution. This may be due to the operations of the system changing or expanding without model re-qualification. Examples include power uprates, load following, inter-reactor shuffling, new fuels, etc.</t>
-  </si>
-  <si>
-    <t>OP.C0703</t>
+    <t>The model is generalized across a range of operating scenarios for which the data quality and hence model efficiency is heterogeneous.</t>
+  </si>
+  <si>
+    <t>Umbrella for non-adversarial failures in the fidelity of AI-generated or AI-processed content -- distinct from OP.C0301 (training-objective misalignment) and OP.C0302 (drift/out-of-distribution/generalization failure).</t>
+  </si>
+  <si>
+    <t>AI-generated content that is factually wrong, fabricated, or attributed to the wrong source/component.</t>
+  </si>
+  <si>
+    <t>OP.C0301.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cascading fault propagation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faults due to goal/objective misalignment are propagated/exacerbated due to, e.g., agentic AI. </t>
+  </si>
+  <si>
+    <t>https://adversa.ai/blog/cascading-failures-in-agentic-ai-complete-owasp-asi08-security-guide-2026/#1-introduction</t>
+  </si>
+  <si>
+    <t>Covertly diverting nuclear material by substituting or supplementing the material stock with a close copy that can subvert probabilistic detection measures. Kept in this taxonomy despite being a deliberate act because it is a physical-domain technique with no home in ATLAS (attacks on AI models).</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/stamp/stamp.jsp?tp=&amp;arnumber=7105107</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1662,18 +1671,18 @@
         <v>38</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>39</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>11</v>
@@ -1682,20 +1691,20 @@
         <v>12</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -1704,20 +1713,20 @@
         <v>12</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>17</v>
@@ -1726,20 +1735,20 @@
         <v>12</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>17</v>
@@ -1748,20 +1757,20 @@
         <v>12</v>
       </c>
       <c r="F13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>17</v>
@@ -1770,20 +1779,20 @@
         <v>12</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>17</v>
@@ -1792,20 +1801,20 @@
         <v>12</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
@@ -1814,20 +1823,20 @@
         <v>12</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>66</v>
+        <v>283</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
@@ -1836,20 +1845,20 @@
         <v>12</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>11</v>
@@ -1858,24 +1867,24 @@
         <v>12</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>74</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>11</v>
@@ -1884,64 +1893,64 @@
         <v>12</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
-      <c r="C20" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>284</v>
+      <c r="C20" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>91</v>
+        <v>291</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
-      <c r="C21" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>287</v>
+      <c r="C21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>275</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>290</v>
+        <v>87</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>17</v>
@@ -1950,20 +1959,20 @@
         <v>12</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8" t="s">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>17</v>
@@ -1972,42 +1981,42 @@
         <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>92</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
-      <c r="C24" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>87</v>
+      <c r="C24" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="G24" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>11</v>
@@ -2016,42 +2025,42 @@
         <v>12</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>101</v>
-      </c>
       <c r="G26" s="8" t="s">
-        <v>102</v>
+        <v>287</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>17</v>
@@ -2060,20 +2069,20 @@
         <v>12</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>106</v>
+        <v>288</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>17</v>
@@ -2082,46 +2091,46 @@
         <v>12</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>107</v>
+      </c>
       <c r="C30" s="12" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>11</v>
@@ -2130,42 +2139,42 @@
         <v>12</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>123</v>
+      <c r="C31" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>17</v>
@@ -2174,68 +2183,68 @@
         <v>12</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
-      <c r="C33" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>136</v>
+      <c r="E34" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
+      <c r="A35" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>126</v>
+      </c>
       <c r="C35" s="15" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>11</v>
@@ -2244,20 +2253,20 @@
         <v>12</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="C36" s="15" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>11</v>
@@ -2266,20 +2275,20 @@
         <v>12</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="C37" s="15" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>11</v>
@@ -2288,20 +2297,20 @@
         <v>12</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A38" s="14"/>
       <c r="B38" s="14"/>
       <c r="C38" s="15" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>11</v>
@@ -2310,68 +2319,68 @@
         <v>12</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
-      <c r="C39" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="14" t="s">
+      <c r="C39" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="H39" s="14" t="s">
+      <c r="E40" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A41" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A40" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="18" t="s">
-        <v>162</v>
       </c>
       <c r="D41" s="18" t="s">
         <v>11</v>
@@ -2380,20 +2389,20 @@
         <v>12</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="18" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D42" s="18" t="s">
         <v>11</v>
@@ -2402,68 +2411,68 @@
         <v>12</v>
       </c>
       <c r="F42" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A44" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G44" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="G42" s="17" t="s">
+      <c r="H44" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="H42" s="17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="45" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A45" s="19"/>
       <c r="B45" s="19"/>
       <c r="C45" s="19" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>17</v>
@@ -2472,83 +2481,108 @@
         <v>12</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A46" s="19"/>
       <c r="B46" s="19"/>
-      <c r="C46" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>185</v>
+      <c r="C46" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>174</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="60" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="19"/>
       <c r="B47" s="19"/>
-      <c r="C47" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>190</v>
+      <c r="C47" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>178</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" s="19"/>
       <c r="B48" s="19"/>
-      <c r="C48" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="D48" s="20" t="s">
+      <c r="C48" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="60" x14ac:dyDescent="0.2">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="D49" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>183</v>
+      <c r="E49" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H48" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="H43" r:id="rId1" xr:uid="{15AFB487-4293-E045-8153-0D7217A7D66E}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2567,54 +2601,54 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C3" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>26</v>
@@ -2623,623 +2657,623 @@
         <v>12</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C11" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E11" s="23"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E12" s="23"/>
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E14" s="23"/>
     </row>
     <row r="15" spans="1:5" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="23" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E16" s="23"/>
     </row>
     <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="23" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E18" s="23"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="23" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E19" s="23"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="23" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E20" s="23"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="23" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E21" s="23"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="23" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C22" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E22" s="23"/>
     </row>
     <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="23" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C23" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="23" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C24" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E24" s="23"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="23" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E25" s="23"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="23" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C26" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E26" s="23"/>
     </row>
     <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="23" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B27" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>43</v>
-      </c>
       <c r="E27" s="23" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="23" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E28" s="23"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="23" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C29" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E29" s="23"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="23" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C30" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E30" s="23"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="23" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C31" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E31" s="23"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="23" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E32" s="23"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="23" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C33" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E33" s="23"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="23" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C34" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E34" s="23"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="23" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C35" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E35" s="23"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="23" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C36" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E36" s="23"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="23" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C37" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E37" s="23"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="23" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C38" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E38" s="23"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="23" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C39" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E39" s="23"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="23" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C40" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E40" s="23"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="23" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C41" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E41" s="23"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="23" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C42" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E42" s="23"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="23" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C43" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E43" s="23"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="23" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C44" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E44" s="23"/>
     </row>
@@ -3260,74 +3294,74 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
